--- a/AMZN_Model.xlsx
+++ b/AMZN_Model.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Input" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="304">
   <si>
     <t xml:space="preserve">DATA INPUT - historical financials. Fixed row keys in column A; one column per year. A Python extractor should write ONLY this tab. (You may hide this tab.)</t>
   </si>
@@ -639,280 +639,196 @@
     <t xml:space="preserve">  none - every historical figure above was read from the source statements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Institutional Valuation Layer - EPS-Power x Multiple (street-comparable lens)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The FCF DCF above is the fundamental anchor. This layer prices FORWARD EPS POWER at scenario multiples - how the street values megacaps. The gap between the two lenses IS the multiple bet: printed, never blended.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS - cash-return convention (today's diluted count)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS - street count-shrink view (buybacks retire stock at today's price)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diluted count, street view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS x Multiple - Scenario Valuation (forward value, discounted at the hurdle)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle (CAPM, 12-mo convention)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor year: 3 (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor EPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PV Today</t>
+    <t xml:space="preserve">Catalyst Odds (judgmental - the odds ARE the thesis; news scan as-of in attestation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS growth re-accelerates on AI workloads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The valuation driver; retail is the ballast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI capex earns its return (AWS margin holds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE swing node - $25B bond sale funds it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail margin expansion continues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-year efficiency programme, well-demonstrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertising keeps compounding &gt;20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest-margin segment; underrated in the blend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt-funded capex stays non-dilutive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bond market open at scale = no equity issuance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Capital Build - the discount rate is DERIVED here, not asserted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government bond yield (United States 10Y, as-of 2026-07-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: sovereign default spread (Aa1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISK-FREE RATE in USD (bond yield less sovereign spread)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity risk premium (Damodaran country ERP table, last updated Jan-2026 (stern.nyu.edu/~adamodar), fetched 2026-07-19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied MARKET RETURN  Rm = rf + ERP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country risk premium (already inside the ERP above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levered beta (adjusted)  [raw 1.461]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size / illiquidity premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of equity = rf + beta x (ERP + CRP) + size premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-1 WACC used in the DCF grid (row 149) - cross-check they agree; the grid fades toward the mature rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of debt - pre-tax (marginal, = rf + credit spread)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marginal: rf-equivalent + credit spread; after-tax at the MARGINAL rate 25% (not the effective rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of debt - after tax  = pre-tax x (1 - tax rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC = CoE x (1-Wd) + Kd(after-tax) x Wd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal growth vs risk-free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damodaran convention for MATURE-MARKET compounders: terminal g = the risk-free rate (an economy cannot outgrow its own bond) - a gap there means one input is stale. For declining or finite-resource industries (coal, EM cyclicals) terminal g SHOULD sit well below rf; the gap is then deliberate, not an error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional premium: none - the model discounts at the derived build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC USED IN THE MODEL (build + named premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tie-out vs the DCF grid (year-1 WACC, row 149)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be 0.00%. A non-zero tie-out means the discount rate is asserted, not derived - any premium above the CAPM build must be NAMED above, never silent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital structure at MARKET values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight of debt   Wd = D / (D + E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market values: gross debt 153.0 / (debt + mcap 2,659.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight of equity We = 1 - Wd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: We + Wd must equal 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity contribution  = CoE x We</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt contribution    = Kd(after-tax) x Wd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum = WACC (must equal the build above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt weight uses GROSS debt at book vs equity at MARKET (standard); a net-debt weight would be negative for net-cash names and is not used. Cost of debt is the MARGINAL rate today, not the legacy coupon - old ZIRP-era bonds understate what new borrowing costs and must never set the WACC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charts and Graphs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Margin (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sensitivity &amp; Scenarios - NASDAQ: AMZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All figures in USD billions | per-share values in USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid 1: Intrinsic Value per Share - WACC (rows) x Perpetual Growth (columns) - perpetuity TV only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid 2: Intrinsic Value per Share - WACC (rows) x Exit EV/EBITDA (columns) - exit-multiple TV only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid 3: Intrinsic Value per Share - WACC (rows) x FCF Deck Scale (columns) - stresses the revenue/margin deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scales every forecast cash flow and the terminal value by the column factor - the growth deck is usually where the real risk lives, not the discount rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenarios: Implied Value per Share - Bear / Base / Bull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear = higher WACC, lower terminal growth; Bull = the reverse. Blue offsets are editable. Terminal value = average of perpetuity and exit-multiple, like the DCF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth</t>
   </si>
   <si>
     <t xml:space="preserve">Prob.</t>
   </si>
   <si>
-    <t xml:space="preserve">Contribution</t>
+    <t xml:space="preserve">Bear implied EV</t>
   </si>
   <si>
     <t xml:space="preserve">Bear</t>
   </si>
   <si>
+    <t xml:space="preserve">Base implied EV</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base</t>
   </si>
   <si>
+    <t xml:space="preserve">Bull implied EV</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme Bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PWFV (EPS-anchored, PV today)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vs DCF PWFV (Sensitivity!B46) and vs price D135 - the spread between the two PWFVs is the multiple bet, held vs faded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor = FY2028 EPS. Base = street avg $13.06 (26 analysts); bear = street low $9.89 (AWS margin compression + retail cycle); bull = street high $15.40; x-bull = AWS AI acceleration. Multiples 20-34x reflect AMZN's structurally higher P/E (heavy D&amp;A depresses EPS vs cash flow). Hurdle 9% ~ CAPM (beta 1.1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street Reconciliation (consensus vs this deck)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street Revenue (consensus avg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck vs Street - Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street EPS (consensus avg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck vs Street - EPS (count-shrink view)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where we differ: Deck 277 sits between price 247 and consensus 309. Street assumes AWS margin expansion carries through the AI capex cycle; the deck models the capex but fades the margin benefit - a deliberate conservatism, named. The $25B bond sale (Jul-2026) funds capex WITHOUT dilution, which the deck reflects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consensus price target: 308.7 (median 319.5, range 175-335) as-of 2026-07-19 - a 12-mo FORWARD value; compare to our PV x (1+hurdle).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: FMP consensus (46 analysts FY27; 34 FY28) (2026-07-19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalyst Odds (judgmental - the odds ARE the thesis; news scan as-of in attestation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS growth re-accelerates on AI workloads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The valuation driver; retail is the ballast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI capex earns its return (AWS margin holds)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE swing node - $25B bond sale funds it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail margin expansion continues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-year efficiency programme, well-demonstrated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advertising keeps compounding &gt;20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highest-margin segment; underrated in the blend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt-funded capex stays non-dilutive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bond market open at scale = no equity issuance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple holds &gt;=25x forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The re-rating bet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of Capital Build - the discount rate is DERIVED here, not asserted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government bond yield (United States 10Y, as-of 2026-07-17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less: sovereign default spread (Aa1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RISK-FREE RATE in USD (bond yield less sovereign spread)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity risk premium (Damodaran country ERP table, last updated Jan-2026 (stern.nyu.edu/~adamodar), fetched 2026-07-19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied MARKET RETURN  Rm = rf + ERP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country risk premium (already inside the ERP above)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levered beta (adjusted)  [raw 1.461]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size / illiquidity premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of equity = rf + beta x (ERP + CRP) + size premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year-1 WACC used in the DCF grid (row 149) - cross-check they agree; the grid fades toward the mature rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of debt - pre-tax (marginal, = rf + credit spread)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marginal: rf-equivalent + credit spread; after-tax at the MARGINAL rate 25% (not the effective rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of debt - after tax  = pre-tax x (1 - tax rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC = CoE x (1-Wd) + Kd(after-tax) x Wd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal growth vs risk-free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damodaran convention for MATURE-MARKET compounders: terminal g = the risk-free rate (an economy cannot outgrow its own bond) - a gap there means one input is stale. For declining or finite-resource industries (coal, EM cyclicals) terminal g SHOULD sit well below rf; the gap is then deliberate, not an error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional premium: none - the model discounts at the derived build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC USED IN THE MODEL (build + named premium)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tie-out vs the DCF grid (year-1 WACC, row 149)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 0.00%. A non-zero tie-out means the discount rate is asserted, not derived - any premium above the CAPM build must be NAMED above, never silent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital structure at MARKET values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight of debt   Wd = D / (D + E)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market values: gross debt 153.0 / (debt + mcap 2,659.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight of equity We = 1 - Wd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: We + Wd must equal 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity contribution  = CoE x We</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt contribution    = Kd(after-tax) x Wd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum = WACC (must equal the build above)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt weight uses GROSS debt at book vs equity at MARKET (standard); a net-debt weight would be negative for net-cash names and is not used. Cost of debt is the MARGINAL rate today, not the legacy coupon - old ZIRP-era bonds understate what new borrowing costs and must never set the WACC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charts and Graphs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross Profit Margin (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sensitivity &amp; Scenarios - NASDAQ: AMZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All figures in USD billions | per-share values in USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid 1: Intrinsic Value per Share - WACC (rows) x Perpetual Growth (columns) - perpetuity TV only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid 2: Intrinsic Value per Share - WACC (rows) x Exit EV/EBITDA (columns) - exit-multiple TV only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid 3: Intrinsic Value per Share - WACC (rows) x FCF Deck Scale (columns) - stresses the revenue/margin deck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scales every forecast cash flow and the terminal value by the column factor - the growth deck is usually where the real risk lives, not the discount rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenarios: Implied Value per Share - Bear / Base / Bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear = higher WACC, lower terminal growth; Bull = the reverse. Blue offsets are editable. Terminal value = average of perpetuity and exit-multiple, like the DCF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear implied EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base implied EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bull implied EV</t>
   </si>
   <si>
     <t xml:space="preserve">Current Price</t>
@@ -1045,6 +961,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1064,78 +981,86 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000CC"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FF2E5B9F"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1153,9 +1078,10 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1419,15 +1345,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1475,7 +1393,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1567,6 +1493,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1778,8 +1705,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="48856931"/>
-        <c:axId val="49674296"/>
+        <c:axId val="12644468"/>
+        <c:axId val="33366433"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1954,7 +1881,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:hiLowLines>
           <c:spPr>
@@ -1964,11 +1891,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2687283"/>
-        <c:axId val="32341806"/>
+        <c:axId val="37284831"/>
+        <c:axId val="97598492"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="48856931"/>
+        <c:axId val="12644468"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +1928,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49674296"/>
+        <c:crossAx val="33366433"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2009,7 +1936,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49674296"/>
+        <c:axId val="33366433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2052,12 +1979,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48856931"/>
+        <c:crossAx val="12644468"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="2687283"/>
+        <c:axId val="37284831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2090,7 +2017,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32341806"/>
+        <c:crossAx val="97598492"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2098,7 +2025,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32341806"/>
+        <c:axId val="97598492"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2131,7 +2058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2687283"/>
+        <c:crossAx val="37284831"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2721,11 +2648,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-20"/>
-        <c:axId val="77494079"/>
-        <c:axId val="82041910"/>
+        <c:axId val="1846653"/>
+        <c:axId val="85338239"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="77494079"/>
+        <c:axId val="1846653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2758,7 +2685,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82041910"/>
+        <c:crossAx val="85338239"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2766,7 +2693,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82041910"/>
+        <c:axId val="85338239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2809,7 +2736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77494079"/>
+        <c:crossAx val="1846653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3036,7 +2963,7 @@
                   <c:v>292.362387160958</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>310.147550795575</c:v>
+                  <c:v>310.147550795576</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>327.4189981338</c:v>
@@ -3045,7 +2972,7 @@
                   <c:v>344.350765999277</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>361.447396122956</c:v>
+                  <c:v>361.447396122957</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>378.660706239099</c:v>
@@ -3175,7 +3102,7 @@
                   <c:v>321.675800980618</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>342.910071767828</c:v>
+                  <c:v>342.910071767829</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>363.707962567148</c:v>
@@ -3187,7 +3114,7 @@
                   <c:v>403.656482237872</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>422.617538188297</c:v>
+                  <c:v>422.617538188298</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>441.037102451247</c:v>
@@ -3509,11 +3436,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77528904"/>
-        <c:axId val="69895986"/>
+        <c:axId val="35962205"/>
+        <c:axId val="65204660"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77528904"/>
+        <c:axId val="35962205"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3546,7 +3473,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69895986"/>
+        <c:crossAx val="65204660"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3554,7 +3481,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69895986"/>
+        <c:axId val="65204660"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3597,7 +3524,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77528904"/>
+        <c:crossAx val="35962205"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4312,8 +4239,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>810360</xdr:colOff>
-      <xdr:row>304</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:row>302</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4321,7 +4248,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="48150720"/>
+        <a:off x="0" y="44517960"/>
         <a:ext cx="5039640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4342,8 +4269,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>105840</xdr:colOff>
-      <xdr:row>304</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:row>302</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4351,7 +4278,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8176320" y="48150720"/>
+        <a:off x="8176320" y="44517960"/>
         <a:ext cx="5039640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4377,8 +4304,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>198720</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4386,7 +4313,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="8706960"/>
+        <a:off x="0" y="9392760"/>
         <a:ext cx="6119640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4443,14 +4370,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -4458,25 +4385,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -4494,12 +4454,48 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -4512,19 +4508,18 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -4547,12 +4542,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -4575,7 +4570,7 @@
         <v>716.924</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -4598,7 +4593,7 @@
         <v>356.414</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -4621,7 +4616,7 @@
         <v>83.0842</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -4644,7 +4639,7 @@
         <v>131.6948</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -4667,7 +4662,7 @@
         <v>65.756</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
@@ -4690,7 +4685,7 @@
         <v>2.274</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -4713,12 +4708,12 @@
         <v>19.087</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -4741,7 +4736,7 @@
         <v>123.029</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -4764,7 +4759,7 @@
         <v>67.729</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -4787,7 +4782,7 @@
         <v>38.325</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -4810,7 +4805,7 @@
         <v>588.959</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -4833,7 +4828,7 @@
         <v>253.99</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -4856,7 +4851,7 @@
         <v>152.987</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -4879,7 +4874,7 @@
         <v>160.529</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
@@ -4902,12 +4897,12 @@
         <v>250.536</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>41</v>
       </c>
@@ -4930,7 +4925,7 @@
         <v>131.819</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
@@ -4953,7 +4948,7 @@
         <v>10.18</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -4976,12 +4971,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
@@ -4992,7 +4987,7 @@
         <v>232.212</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
@@ -5003,7 +4998,7 @@
         <v>110.104</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>52</v>
       </c>
@@ -5031,8 +5026,8 @@
     <tabColor rgb="FF2E5B9F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S286"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S282"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="2"/>
@@ -5117,7 +5112,7 @@
       </c>
       <c r="S2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
         <v>72</v>
       </c>
@@ -5182,7 +5177,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
         <v>73</v>
       </c>
@@ -5215,8 +5210,7 @@
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>77</v>
       </c>
@@ -5239,7 +5233,7 @@
       <c r="R7" s="19"/>
       <c r="S7" s="19"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>78</v>
       </c>
@@ -5290,7 +5284,7 @@
         <v>0.043</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
@@ -5345,7 +5339,7 @@
         <v>0.497</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>80</v>
       </c>
@@ -5400,7 +5394,7 @@
         <v>0.0998</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>81</v>
       </c>
@@ -5455,7 +5449,7 @@
         <v>233.02</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
@@ -5510,7 +5504,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -5565,7 +5559,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
@@ -5620,7 +5614,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
@@ -5675,7 +5669,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>86</v>
       </c>
@@ -5730,7 +5724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>87</v>
       </c>
@@ -5785,7 +5779,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>88</v>
       </c>
@@ -5840,7 +5834,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>89</v>
       </c>
@@ -5895,7 +5889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>90</v>
       </c>
@@ -5950,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -6000,8 +5994,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
         <v>92</v>
@@ -6025,8 +6017,7 @@
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -6091,7 +6082,7 @@
         <v>1472.75881175029</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>93</v>
       </c>
@@ -6156,7 +6147,7 @@
         <v>731.961129439893</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -6221,12 +6212,12 @@
         <v>740.797682310394</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>96</v>
       </c>
@@ -6291,7 +6282,7 @@
         <v>146.981329412679</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
@@ -6356,7 +6347,7 @@
         <v>233.02</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
@@ -6421,7 +6412,7 @@
         <v>99.8942745189304</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>20</v>
       </c>
@@ -6486,7 +6477,7 @@
         <v>3.05974</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>99</v>
       </c>
@@ -6551,7 +6542,7 @@
         <v>482.955343931609</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>100</v>
       </c>
@@ -6616,8 +6607,7 @@
         <v>257.842338378785</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>22</v>
       </c>
@@ -6682,7 +6672,7 @@
         <v>51.5684676757571</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>101</v>
       </c>
@@ -6747,8 +6737,6 @@
         <v>206.273870703028</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
         <v>102</v>
@@ -6772,13 +6760,12 @@
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>25</v>
       </c>
@@ -6843,7 +6830,7 @@
         <v>1380.17357743146</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>27</v>
       </c>
@@ -6908,7 +6895,7 @@
         <v>137.188492053451</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>29</v>
       </c>
@@ -6973,7 +6960,7 @@
         <v>78.2095453374132</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>104</v>
       </c>
@@ -7038,7 +7025,7 @@
         <v>794.259921632513</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>105</v>
       </c>
@@ -7103,13 +7090,12 @@
         <v>2389.83153645483</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>33</v>
       </c>
@@ -7174,7 +7160,7 @@
         <v>521.396968916088</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>35</v>
       </c>
@@ -7239,7 +7225,7 @@
         <v>152.987</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>107</v>
       </c>
@@ -7304,12 +7290,12 @@
         <v>674.383968916088</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
@@ -7374,7 +7360,7 @@
         <v>160.529</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>39</v>
       </c>
@@ -7439,7 +7425,7 @@
         <v>1554.91856753875</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>108</v>
       </c>
@@ -7504,7 +7490,7 @@
         <v>1715.44756753875</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>109</v>
       </c>
@@ -7569,8 +7555,7 @@
         <v>2389.83153645483</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
         <v>110</v>
       </c>
@@ -7635,8 +7620,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
         <v>111</v>
@@ -7660,13 +7643,12 @@
       <c r="R63" s="16"/>
       <c r="S63" s="16"/>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>101</v>
       </c>
@@ -7727,7 +7709,7 @@
         <v>206.273870703028</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
         <v>113</v>
       </c>
@@ -7788,7 +7770,7 @@
         <v>99.8942745189304</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>114</v>
       </c>
@@ -7849,7 +7831,7 @@
         <v>-12.6154880686333</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>115</v>
       </c>
@@ -7910,13 +7892,12 @@
         <v>318.783633290592</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>117</v>
       </c>
@@ -7977,7 +7958,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>118</v>
       </c>
@@ -8038,13 +8019,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>120</v>
       </c>
@@ -8105,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>121</v>
       </c>
@@ -8166,7 +8146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>122</v>
       </c>
@@ -8227,8 +8207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>123</v>
       </c>
@@ -8289,7 +8268,7 @@
         <v>223.783633290592</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>124</v>
       </c>
@@ -8350,7 +8329,7 @@
         <v>1156.38994414086</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>125</v>
       </c>
@@ -8411,13 +8390,11 @@
         <v>1380.17357743146</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="86" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="s">
         <v>127</v>
@@ -8441,13 +8418,12 @@
       <c r="R86" s="16"/>
       <c r="S86" s="16"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>27</v>
       </c>
@@ -8512,7 +8488,7 @@
         <v>137.188492053451</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>29</v>
       </c>
@@ -8577,7 +8553,7 @@
         <v>78.2095453374132</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
         <v>33</v>
       </c>
@@ -8642,7 +8618,7 @@
         <v>521.396968916088</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>129</v>
       </c>
@@ -8707,7 +8683,7 @@
         <v>-305.998931525223</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
         <v>130</v>
       </c>
@@ -8772,13 +8748,12 @@
         <v>-12.6154880686333</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>132</v>
       </c>
@@ -8843,7 +8818,7 @@
         <v>799.154196151443</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>133</v>
       </c>
@@ -8908,7 +8883,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>134</v>
       </c>
@@ -8973,7 +8948,7 @@
         <v>99.8942745189304</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>135</v>
       </c>
@@ -9038,13 +9013,12 @@
         <v>794.259921632513</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>137</v>
       </c>
@@ -9109,7 +9083,7 @@
         <v>152.987</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>138</v>
       </c>
@@ -9174,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>139</v>
       </c>
@@ -9239,7 +9213,7 @@
         <v>152.987</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>140</v>
       </c>
@@ -9304,13 +9278,12 @@
         <v>3.05974</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>142</v>
       </c>
@@ -9355,7 +9328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>143</v>
       </c>
@@ -9400,7 +9373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>144</v>
       </c>
@@ -9445,8 +9418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="18" t="s">
         <v>145</v>
       </c>
@@ -9469,28 +9441,26 @@
       <c r="R112" s="19"/>
       <c r="S112" s="19"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="128" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="129" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="131" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="15" t="s">
         <v>147</v>
@@ -9514,8 +9484,7 @@
       <c r="R131" s="16"/>
       <c r="S131" s="16"/>
     </row>
-    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="18" t="s">
         <v>148</v>
       </c>
@@ -9538,7 +9507,7 @@
       <c r="R133" s="19"/>
       <c r="S133" s="19"/>
     </row>
-    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>149</v>
       </c>
@@ -9546,7 +9515,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
         <v>150</v>
       </c>
@@ -9554,7 +9523,7 @@
         <v>247.23</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>151</v>
       </c>
@@ -9562,7 +9531,7 @@
         <v>10.757</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
         <v>152</v>
       </c>
@@ -9571,7 +9540,7 @@
         <v>2659.45311</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>153</v>
       </c>
@@ -9579,7 +9548,7 @@
         <v>0.0432</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
         <v>154</v>
       </c>
@@ -9587,7 +9556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>155</v>
       </c>
@@ -9595,7 +9564,7 @@
         <v>2659.45</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
         <v>156</v>
       </c>
@@ -9603,8 +9572,7 @@
         <v>10.757</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="18" t="s">
         <v>157</v>
       </c>
@@ -9627,7 +9595,7 @@
       <c r="R143" s="19"/>
       <c r="S143" s="19"/>
     </row>
-    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H144" s="2" t="s">
         <v>158</v>
       </c>
@@ -9635,7 +9603,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
         <v>160</v>
       </c>
@@ -9686,7 +9654,7 @@
         <v>49674</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
         <v>161</v>
       </c>
@@ -9721,7 +9689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
         <v>162</v>
       </c>
@@ -9766,7 +9734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
         <v>163</v>
       </c>
@@ -9811,7 +9779,7 @@
         <v>9.46027397260274</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
         <v>164</v>
       </c>
@@ -9846,7 +9814,7 @@
         <v>0.085</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
         <v>165</v>
       </c>
@@ -9891,7 +9859,7 @@
         <v>0.438155683007417</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
         <v>166</v>
       </c>
@@ -9936,7 +9904,7 @@
         <v>260.902078378785</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>167</v>
       </c>
@@ -9981,7 +9949,7 @@
         <v>-52.1804156757571</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
         <v>168</v>
       </c>
@@ -10026,7 +9994,7 @@
         <v>99.8942745189304</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>169</v>
       </c>
@@ -10071,7 +10039,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
         <v>170</v>
       </c>
@@ -10116,7 +10084,7 @@
         <v>12.6154880686333</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
         <v>171</v>
       </c>
@@ -10161,7 +10129,7 @@
         <v>226.231425290592</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
         <v>172</v>
       </c>
@@ -10174,7 +10142,7 @@
         <v>5168.19809841823</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>173</v>
       </c>
@@ -10183,7 +10151,7 @@
       </c>
       <c r="I158" s="29" t="n">
         <f aca="false">I156*I147</f>
-        <v>10.6305508131045</v>
+        <v>10.6305508131044</v>
       </c>
       <c r="J158" s="29" t="n">
         <f aca="false">J156*J147</f>
@@ -10226,7 +10194,7 @@
         <v>5168.19809841823</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
         <v>173</v>
       </c>
@@ -10236,7 +10204,7 @@
       </c>
       <c r="I159" s="22" t="n">
         <f aca="false">I158</f>
-        <v>10.6305508131045</v>
+        <v>10.6305508131044</v>
       </c>
       <c r="J159" s="22" t="n">
         <f aca="false">J158</f>
@@ -10279,8 +10247,7 @@
         <v>5168.19809841823</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="18" t="s">
         <v>174</v>
       </c>
@@ -10303,7 +10270,7 @@
       <c r="R161" s="19"/>
       <c r="S161" s="19"/>
     </row>
-    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>175</v>
       </c>
@@ -10312,7 +10279,7 @@
         <v>5646.04360916616</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
         <v>176</v>
       </c>
@@ -10321,7 +10288,7 @@
         <v>4690.3525876703</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>177</v>
       </c>
@@ -10330,7 +10297,7 @@
         <v>5168.19809841823</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
         <v>178</v>
       </c>
@@ -10346,7 +10313,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="18" t="s">
         <v>180</v>
       </c>
@@ -10369,7 +10336,7 @@
       <c r="R166" s="19"/>
       <c r="S166" s="19"/>
     </row>
-    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
         <v>181</v>
       </c>
@@ -10378,7 +10345,7 @@
         <v>2991.53374812283</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
         <v>182</v>
       </c>
@@ -10387,7 +10354,7 @@
         <v>123.029</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
         <v>183</v>
       </c>
@@ -10396,7 +10363,7 @@
         <v>152.987</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
         <v>184</v>
       </c>
@@ -10405,7 +10372,7 @@
         <v>2961.57574812283</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
         <v>185</v>
       </c>
@@ -10414,8 +10381,7 @@
         <v>275.316142802159</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="18" t="s">
         <v>186</v>
       </c>
@@ -10438,7 +10404,7 @@
       <c r="R173" s="19"/>
       <c r="S173" s="19"/>
     </row>
-    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
         <v>187</v>
       </c>
@@ -10447,7 +10413,7 @@
         <v>2659.45311</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
         <v>188</v>
       </c>
@@ -10456,7 +10422,7 @@
         <v>152.987</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>189</v>
       </c>
@@ -10465,7 +10431,7 @@
         <v>123.029</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
         <v>190</v>
       </c>
@@ -10474,7 +10440,7 @@
         <v>2689.41111</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
         <v>150</v>
       </c>
@@ -10483,8 +10449,7 @@
         <v>247.23</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="18" t="s">
         <v>191</v>
       </c>
@@ -10507,7 +10472,7 @@
       <c r="R180" s="19"/>
       <c r="S180" s="19"/>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
         <v>192</v>
       </c>
@@ -10516,7 +10481,7 @@
         <v>0.113603295725273</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
         <v>193</v>
       </c>
@@ -10525,7 +10490,7 @@
         <v>0.104989934001134</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
         <v>194</v>
       </c>
@@ -10537,7 +10502,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="18" t="s">
         <v>196</v>
       </c>
@@ -10560,7 +10525,7 @@
       <c r="R184" s="19"/>
       <c r="S184" s="19"/>
     </row>
-    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
         <v>197</v>
       </c>
@@ -10605,7 +10570,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
         <v>198</v>
       </c>
@@ -10647,10 +10612,10 @@
       </c>
       <c r="R186" s="22" t="n">
         <f aca="false">Q186*(1+R149)^R147-R158</f>
-        <v>5168.19809841823</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5168.19809841824</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
         <v>199</v>
       </c>
@@ -10668,7 +10633,7 @@
       </c>
       <c r="L187" s="25" t="n">
         <f aca="false">L186+$H$44-$H$52</f>
-        <v>3837.27425095368</v>
+        <v>3837.27425095369</v>
       </c>
       <c r="M187" s="25" t="n">
         <f aca="false">M186+$H$44-$H$52</f>
@@ -10695,7 +10660,7 @@
         <v>5138.24009841823</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
         <v>200</v>
       </c>
@@ -10740,541 +10705,133 @@
         <v>477.664785573881</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="200" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="15" t="s">
+      <c r="A200" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="B200" s="16"/>
-      <c r="C200" s="16"/>
-      <c r="D200" s="16"/>
-      <c r="E200" s="16"/>
-      <c r="F200" s="16"/>
-      <c r="G200" s="16"/>
-      <c r="H200" s="16"/>
-      <c r="I200" s="16"/>
-      <c r="J200" s="16"/>
-      <c r="K200" s="16"/>
-      <c r="L200" s="16"/>
-      <c r="M200" s="16"/>
-      <c r="N200" s="16"/>
-      <c r="O200" s="16"/>
-      <c r="P200" s="16"/>
-      <c r="Q200" s="16"/>
-      <c r="R200" s="16"/>
-      <c r="S200" s="16"/>
-    </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="s">
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
         <v>206</v>
       </c>
+      <c r="F201" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I202" s="25" t="n">
-        <f aca="false">I38/$D$136</f>
-        <v>6.25633431179697</v>
-      </c>
-      <c r="J202" s="25" t="n">
-        <f aca="false">J38/$D$136</f>
-        <v>7.01914664371107</v>
-      </c>
-      <c r="K202" s="25" t="n">
-        <f aca="false">K38/$D$136</f>
-        <v>8.11338701055038</v>
-      </c>
-      <c r="L202" s="25" t="n">
-        <f aca="false">L38/$D$136</f>
-        <v>9.4085189225112</v>
-      </c>
-      <c r="M202" s="25" t="n">
-        <f aca="false">M38/$D$136</f>
-        <v>10.8740138551919</v>
-      </c>
-      <c r="N202" s="25" t="n">
-        <f aca="false">N38/$D$136</f>
-        <v>12.4954099062614</v>
-      </c>
-      <c r="O202" s="25" t="n">
-        <f aca="false">O38/$D$136</f>
-        <v>14.2669990120174</v>
-      </c>
-      <c r="P202" s="25" t="n">
-        <f aca="false">P38/$D$136</f>
-        <v>16.0242966380935</v>
-      </c>
-      <c r="Q202" s="25" t="n">
-        <f aca="false">Q38/$D$136</f>
-        <v>17.6250671530331</v>
-      </c>
-      <c r="R202" s="25" t="n">
-        <f aca="false">R38/$D$136</f>
-        <v>19.1757804874062</v>
+      <c r="A202" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F202" s="21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="I203" s="22" t="n">
-        <f aca="false">I38/I204</f>
-        <v>6.25633431179697</v>
-      </c>
-      <c r="J203" s="22" t="n">
-        <f aca="false">J38/J204</f>
-        <v>7.01914664371107</v>
-      </c>
-      <c r="K203" s="22" t="n">
-        <f aca="false">K38/K204</f>
-        <v>8.11338701055038</v>
-      </c>
-      <c r="L203" s="22" t="n">
-        <f aca="false">L38/L204</f>
-        <v>9.4085189225112</v>
-      </c>
-      <c r="M203" s="22" t="n">
-        <f aca="false">M38/M204</f>
-        <v>10.8740138551919</v>
-      </c>
-      <c r="N203" s="22" t="n">
-        <f aca="false">N38/N204</f>
-        <v>12.4954099062614</v>
-      </c>
-      <c r="O203" s="22" t="n">
-        <f aca="false">O38/O204</f>
-        <v>14.2669990120174</v>
-      </c>
-      <c r="P203" s="22" t="n">
-        <f aca="false">P38/P204</f>
-        <v>16.0242966380935</v>
-      </c>
-      <c r="Q203" s="22" t="n">
-        <f aca="false">Q38/Q204</f>
-        <v>17.6250671530331</v>
-      </c>
-      <c r="R203" s="22" t="n">
-        <f aca="false">R38/R204</f>
-        <v>19.1757804874062</v>
+        <v>211</v>
+      </c>
+      <c r="F203" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I204" s="41" t="n">
-        <f aca="false">$D$136+I77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="J204" s="41" t="n">
-        <f aca="false">I204+J77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="K204" s="41" t="n">
-        <f aca="false">J204+K77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="L204" s="41" t="n">
-        <f aca="false">K204+L77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="M204" s="41" t="n">
-        <f aca="false">L204+M77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="N204" s="41" t="n">
-        <f aca="false">M204+N77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="O204" s="41" t="n">
-        <f aca="false">N204+O77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="P204" s="41" t="n">
-        <f aca="false">O204+P77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="Q204" s="41" t="n">
-        <f aca="false">P204+Q77/$D$135</f>
-        <v>10.757</v>
-      </c>
-      <c r="R204" s="41" t="n">
-        <f aca="false">Q204+R77/$D$135</f>
-        <v>10.757</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="206" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="42" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D207" s="31" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="2" t="s">
+      <c r="A204" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="F204" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G204" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E208" s="2" t="s">
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F208" s="2" t="s">
+      <c r="F205" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G205" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G208" s="2" t="s">
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="H208" s="2" t="s">
+      <c r="F206" s="21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G206" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I208" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D209" s="4" t="n">
-        <v>9.89</v>
-      </c>
-      <c r="E209" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="F209" s="22" t="n">
-        <f aca="false">D209*E209</f>
-        <v>197.8</v>
-      </c>
-      <c r="G209" s="22" t="n">
-        <f aca="false">F209/(1+$D$207)^K148</f>
-        <v>160.009898045997</v>
-      </c>
-      <c r="H209" s="21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I209" s="41" t="n">
-        <f aca="false">G209*H209</f>
-        <v>32.0019796091994</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D210" s="4" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="E210" s="32" t="n">
-        <v>25</v>
-      </c>
-      <c r="F210" s="22" t="n">
-        <f aca="false">D210*E210</f>
-        <v>326.5</v>
-      </c>
-      <c r="G210" s="22" t="n">
-        <f aca="false">F210/(1+$D$207)^K148</f>
-        <v>264.121495005147</v>
-      </c>
-      <c r="H210" s="21" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I210" s="41" t="n">
-        <f aca="false">G210*H210</f>
-        <v>118.854672752316</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D211" s="4" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="E211" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="F211" s="22" t="n">
-        <f aca="false">D211*E211</f>
-        <v>462</v>
-      </c>
-      <c r="G211" s="22" t="n">
-        <f aca="false">F211/(1+$D$207)^K148</f>
-        <v>373.733937802076</v>
-      </c>
-      <c r="H211" s="21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I211" s="41" t="n">
-        <f aca="false">G211*H211</f>
-        <v>112.120181340623</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D212" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E212" s="32" t="n">
-        <v>34</v>
-      </c>
-      <c r="F212" s="22" t="n">
-        <f aca="false">D212*E212</f>
-        <v>578</v>
-      </c>
-      <c r="G212" s="22" t="n">
-        <f aca="false">F212/(1+$D$207)^K148</f>
-        <v>467.571896211256</v>
-      </c>
-      <c r="H212" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I212" s="41" t="n">
-        <f aca="false">G212*H212</f>
-        <v>23.3785948105628</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D214" s="25" t="n">
-        <f aca="false">SUM(I209:I212)</f>
-        <v>286.355428512701</v>
-      </c>
-      <c r="E214" s="43" t="n">
-        <f aca="false">SUM(H209:H212)</f>
-        <v>1</v>
-      </c>
-      <c r="F214" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="226" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="42" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I227" s="4" t="n">
-        <v>788.6</v>
-      </c>
-      <c r="J227" s="4" t="n">
-        <v>933.5</v>
-      </c>
-      <c r="K227" s="4" t="n">
-        <v>1067.2</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="I228" s="43" t="n">
-        <f aca="false">I26/I227-1</f>
-        <v>2.07963479583739E-005</v>
-      </c>
-      <c r="J228" s="43" t="n">
-        <f aca="false">J26/J227-1</f>
-        <v>-0.0749491612212105</v>
-      </c>
-      <c r="K228" s="43" t="n">
-        <f aca="false">K26/K227-1</f>
-        <v>-0.118016206690405</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="I229" s="4" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J229" s="4" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="K229" s="4" t="n">
-        <v>13.06</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="I230" s="43" t="n">
-        <f aca="false">I203/I229-1</f>
-        <v>-0.237032401000369</v>
-      </c>
-      <c r="J230" s="43" t="n">
-        <f aca="false">J203/J229-1</f>
-        <v>-0.304346219652025</v>
-      </c>
-      <c r="K230" s="43" t="n">
-        <f aca="false">K203/K229-1</f>
-        <v>-0.378760565807781</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="235" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="42" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F237" s="21" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F238" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F239" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F240" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F241" s="21" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F242" s="21" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="244" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="15" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="B244" s="16"/>
       <c r="C244" s="16"/>
@@ -11297,7 +10854,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="D245" s="31" t="n">
         <v>0.0455</v>
@@ -11305,7 +10862,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="D246" s="31" t="n">
         <v>-0.0023</v>
@@ -11313,7 +10870,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="D247" s="31" t="n">
         <v>0.0432</v>
@@ -11321,7 +10878,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="D248" s="31" t="n">
         <v>0.0446</v>
@@ -11329,7 +10886,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="D249" s="31" t="n">
         <v>0.0878</v>
@@ -11337,7 +10894,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="D250" s="31" t="n">
         <v>0</v>
@@ -11345,7 +10902,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D251" s="4" t="n">
         <v>1.309</v>
@@ -11353,7 +10910,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="D252" s="31" t="n">
         <v>0</v>
@@ -11361,59 +10918,59 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D253" s="44" t="n">
+        <v>228</v>
+      </c>
+      <c r="D253" s="42" t="n">
         <f aca="false">D247+D251*D248+D252</f>
         <v>0.1015814</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="D254" s="31" t="n">
         <v>0.0487</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D255" s="45" t="n">
+        <v>232</v>
+      </c>
+      <c r="D255" s="43" t="n">
         <v>0.0365</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D256" s="44" t="n">
+        <v>233</v>
+      </c>
+      <c r="D256" s="42" t="n">
         <f aca="false">D253*(1-D262)+D255*D262</f>
         <v>0.09804097184</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D257" s="46" t="n">
+        <v>234</v>
+      </c>
+      <c r="D257" s="44" t="n">
         <f aca="false">$D$138-D247</f>
         <v>0</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="D258" s="31" t="n">
         <v>0</v>
@@ -11421,100 +10978,98 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D259" s="44" t="n">
+        <v>237</v>
+      </c>
+      <c r="D259" s="42" t="n">
         <f aca="false">D256+D258</f>
         <v>0.09804097184</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D260" s="46" t="n">
+        <v>238</v>
+      </c>
+      <c r="D260" s="44" t="n">
         <f aca="false">I149-D259</f>
         <v>-4.09718400000009E-005</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="D262" s="31" t="n">
         <v>0.0544</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D263" s="44" t="n">
+        <v>243</v>
+      </c>
+      <c r="D263" s="42" t="n">
         <f aca="false">1-D262</f>
         <v>0.9456</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D264" s="46" t="n">
+        <v>244</v>
+      </c>
+      <c r="D264" s="44" t="n">
         <f aca="false">D262+D263</f>
         <v>1</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D265" s="45" t="n">
+        <v>245</v>
+      </c>
+      <c r="D265" s="43" t="n">
         <f aca="false">D253*D263</f>
         <v>0.09605537184</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D266" s="45" t="n">
+        <v>246</v>
+      </c>
+      <c r="D266" s="43" t="n">
         <f aca="false">D255*D262</f>
         <v>0.0019856</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D267" s="44" t="n">
+        <v>247</v>
+      </c>
+      <c r="D267" s="42" t="n">
         <f aca="false">D265+D266</f>
         <v>0.09804097184</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>248</v>
+      </c>
+    </row>
     <row r="271" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="272" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="273" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="274" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="275" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="15" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="B275" s="16"/>
       <c r="C275" s="16"/>
@@ -11535,7 +11090,6 @@
       <c r="R275" s="16"/>
       <c r="S275" s="16"/>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
         <v>10</v>
@@ -11603,7 +11157,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="D278" s="20" t="n">
         <f aca="false">D28/D26</f>
@@ -11666,7 +11220,6 @@
         <v>0.503</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
         <v>112</v>
@@ -11850,10 +11403,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C2"/>
@@ -11878,48 +11427,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P130"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>252</v>
+      </c>
+    </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -11931,164 +11479,161 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="48" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+-0.005</f>
         <v>0.0382</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+-0.0025</f>
         <v>0.0407</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+0</f>
         <v>0.0432</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+0.0025</f>
         <v>0.0457</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="46" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$138+0.005</f>
         <v>0.0482</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
         <v>0.065</v>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A8-B$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>525.3323115964</v>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A8-C$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>572.721091714611</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A8-D$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>630.978858098466</v>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A8-E$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>704.329310073994</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A8)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A8-F$7)*(1+$A8)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>799.510253708906</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.01</f>
         <v>0.075</v>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A9-B$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>371.243674401651</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A9-C$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>393.8346829724</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A9-D$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>419.977736915909</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A9-E$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>450.582062863429</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A9)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A9-F$7)*(1+$A9)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>486.896151114591</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0</f>
         <v>0.085</v>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A10-B$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>283.461364544152</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A10-C$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>296.179015477945</v>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="48" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A10-D$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>310.417916523435</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A10-E$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>326.468382587435</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A10)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A10-F$7)*(1+$A10)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>344.699618497088</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.01</f>
         <v>0.095</v>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A11-B$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>226.938333208095</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A11-C$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>234.848749874729</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A11-D$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>243.522720273664</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A11-E$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>253.076403694803</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A11)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A11-F$7)*(1+$A11)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>263.650779789141</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
         <v>0.105</v>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+B$7)/($A12-B$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>187.615600235258</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+C$7)/($A12-C$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>192.87525918364</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+D$7)/($A12-D$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>198.560456881891</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+E$7)/($A12-E$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>204.725013576622</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A12)^-('Financial Model &amp; DCF'!$I$148:$R$148))+'Financial Model &amp; DCF'!$R$156*(1+F$7)/($A12-F$7)*(1+$A12)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>211.432224909973</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -12100,164 +11645,161 @@
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="51" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+-1</f>
         <v>12</v>
       </c>
-      <c r="C17" s="51" t="n">
+      <c r="C17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+-0.5</f>
         <v>12.5</v>
       </c>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+0</f>
         <v>13</v>
       </c>
-      <c r="E17" s="51" t="n">
+      <c r="E17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+0.5</f>
         <v>13.5</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="49" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139+1</f>
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
         <v>0.065</v>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>298.133077528173</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>307.375933634564</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>316.618789740955</v>
-      </c>
-      <c r="E18" s="49" t="n">
+        <v>316.618789740956</v>
+      </c>
+      <c r="E18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>325.861645847347</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A18)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A18)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>335.104501953738</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.01</f>
         <v>0.075</v>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>274.963107421116</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>283.423846415014</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>291.884585408912</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>300.34532440281</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A19)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A19)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>308.806063396708</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0</f>
         <v>0.085</v>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>253.852563774496</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>261.603710260648</v>
       </c>
-      <c r="D20" s="50" t="n">
+      <c r="D20" s="48" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>269.354856746801</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>277.106003232953</v>
-      </c>
-      <c r="F20" s="49" t="n">
+        <v>277.106003232954</v>
+      </c>
+      <c r="F20" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A20)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A20)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>284.857149719106</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.01</f>
         <v>0.095</v>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>234.5990739086</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>241.705849609374</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>248.812625310147</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>255.91940101092</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A21)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A21)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>263.026176711694</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="44" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
         <v>0.105</v>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+B$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>217.021880478339</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+C$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>223.542996759501</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+D$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>230.064113040662</v>
-      </c>
-      <c r="E22" s="49" t="n">
+        <v>230.064113040663</v>
+      </c>
+      <c r="E22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+E$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>236.585229321824</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="47" t="n">
         <f aca="false">(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A22)^-('Financial Model &amp; DCF'!$I$148:$R$148))+F$17*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153)*(1+$A22)^-'Financial Model &amp; DCF'!$R$148-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>243.106345602986</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -12269,163 +11811,161 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="52" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="50" t="n">
         <v>0.7</v>
       </c>
-      <c r="C28" s="52" t="n">
+      <c r="C28" s="50" t="n">
         <v>0.85</v>
       </c>
-      <c r="D28" s="52" t="n">
+      <c r="D28" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="52" t="n">
+      <c r="E28" s="50" t="n">
         <v>1.15</v>
       </c>
-      <c r="F28" s="52" t="n">
+      <c r="F28" s="50" t="n">
         <v>1.3</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="44" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.02</f>
         <v>0.065</v>
       </c>
-      <c r="B29" s="49" t="n">
+      <c r="B29" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>330.823683576558</v>
       </c>
-      <c r="C29" s="49" t="n">
+      <c r="C29" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>402.311253748134</v>
       </c>
-      <c r="D29" s="49" t="n">
+      <c r="D29" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>473.798823919711</v>
       </c>
-      <c r="E29" s="49" t="n">
+      <c r="E29" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>545.286394091287</v>
-      </c>
-      <c r="F29" s="49" t="n">
+        <v>545.286394091288</v>
+      </c>
+      <c r="F29" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A29)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A29-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A29)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>616.773964262864</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="44" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+-0.01</f>
         <v>0.075</v>
       </c>
-      <c r="B30" s="49" t="n">
+      <c r="B30" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>248.316319646447</v>
       </c>
-      <c r="C30" s="49" t="n">
+      <c r="C30" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>302.123740404429</v>
       </c>
-      <c r="D30" s="49" t="n">
+      <c r="D30" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>355.93116116241</v>
       </c>
-      <c r="E30" s="49" t="n">
+      <c r="E30" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>409.738581920392</v>
       </c>
-      <c r="F30" s="49" t="n">
+      <c r="F30" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A30)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A30-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A30)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>463.546002678374</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="44" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0</f>
         <v>0.085</v>
       </c>
-      <c r="B31" s="49" t="n">
+      <c r="B31" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>202.084977477343</v>
       </c>
-      <c r="C31" s="49" t="n">
+      <c r="C31" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>245.98568205623</v>
       </c>
-      <c r="D31" s="50" t="n">
+      <c r="D31" s="48" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>289.886386635118</v>
       </c>
-      <c r="E31" s="49" t="n">
+      <c r="E31" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>333.787091214005</v>
-      </c>
-      <c r="F31" s="49" t="n">
+        <v>333.787091214006</v>
+      </c>
+      <c r="F31" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A31)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A31-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A31)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>377.687795792893</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="44" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.01</f>
         <v>0.095</v>
       </c>
-      <c r="B32" s="49" t="n">
+      <c r="B32" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>171.481877787094</v>
       </c>
-      <c r="C32" s="49" t="n">
+      <c r="C32" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>208.8247752895</v>
       </c>
-      <c r="D32" s="49" t="n">
+      <c r="D32" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>246.167672791906</v>
       </c>
-      <c r="E32" s="49" t="n">
+      <c r="E32" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>283.510570294311</v>
       </c>
-      <c r="F32" s="49" t="n">
+      <c r="F32" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A32)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A32-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A32)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>320.853467796717</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="44" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="42" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$R$149+0.02</f>
         <v>0.105</v>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B33" s="47" t="n">
         <f aca="false">(B$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>149.183106305654</v>
       </c>
-      <c r="C33" s="49" t="n">
+      <c r="C33" s="47" t="n">
         <f aca="false">(C$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>181.747695633465</v>
       </c>
-      <c r="D33" s="49" t="n">
+      <c r="D33" s="47" t="n">
         <f aca="false">(D$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>214.312284961277</v>
       </c>
-      <c r="E33" s="49" t="n">
+      <c r="E33" s="47" t="n">
         <f aca="false">(E$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>246.876874289088</v>
       </c>
-      <c r="F33" s="49" t="n">
+      <c r="F33" s="47" t="n">
         <f aca="false">(F$28*(SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$A33)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+'Financial Model &amp; DCF'!$D$138)/($A33-'Financial Model &amp; DCF'!$D$138)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$A33)^-'Financial Model &amp; DCF'!$R$148)-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>279.4414636169</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -12437,111 +11977,110 @@
       <c r="I35" s="16"/>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="53" t="s">
-        <v>291</v>
-      </c>
-      <c r="C38" s="54" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!I$145)</f>
         <v>2026</v>
       </c>
-      <c r="D38" s="54" t="n">
+      <c r="D38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!J$145)</f>
         <v>2027</v>
       </c>
-      <c r="E38" s="54" t="n">
+      <c r="E38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!K$145)</f>
         <v>2028</v>
       </c>
-      <c r="F38" s="54" t="n">
+      <c r="F38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!L$145)</f>
         <v>2029</v>
       </c>
-      <c r="G38" s="54" t="n">
+      <c r="G38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!M$145)</f>
         <v>2030</v>
       </c>
-      <c r="H38" s="54" t="n">
+      <c r="H38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!N$145)</f>
         <v>2031</v>
       </c>
-      <c r="I38" s="54" t="n">
+      <c r="I38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!O$145)</f>
         <v>2032</v>
       </c>
-      <c r="J38" s="54" t="n">
+      <c r="J38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!P$145)</f>
         <v>2033</v>
       </c>
-      <c r="K38" s="54" t="n">
+      <c r="K38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!Q$145)</f>
         <v>2034</v>
       </c>
-      <c r="L38" s="54" t="n">
+      <c r="L38" s="52" t="n">
         <f aca="false">YEAR('Financial Model &amp; DCF'!R$145)</f>
         <v>2035</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B39" s="41" t="n">
+        <v>263</v>
+      </c>
+      <c r="B39" s="53" t="n">
         <f aca="false">SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$N39)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+$O39)/($N39-$O39)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$N39)^-'Financial Model &amp; DCF'!$R$148</f>
         <v>2276.44833785454</v>
       </c>
-      <c r="C39" s="41" t="n">
+      <c r="C39" s="53" t="n">
         <f aca="false">B39*(1+$N39)^'Financial Model &amp; DCF'!I$147-'Financial Model &amp; DCF'!I$158</f>
         <v>2372.87587313875</v>
       </c>
-      <c r="D39" s="41" t="n">
+      <c r="D39" s="53" t="n">
         <f aca="false">C39*(1+$N39)^'Financial Model &amp; DCF'!J$147-'Financial Model &amp; DCF'!J$158</f>
         <v>2577.21667295775</v>
       </c>
-      <c r="E39" s="41" t="n">
+      <c r="E39" s="53" t="n">
         <f aca="false">D39*(1+$N39)^'Financial Model &amp; DCF'!K$147-'Financial Model &amp; DCF'!K$158</f>
         <v>2779.57238422871</v>
       </c>
-      <c r="F39" s="41" t="n">
+      <c r="F39" s="53" t="n">
         <f aca="false">E39*(1+$N39)^'Financial Model &amp; DCF'!L$147-'Financial Model &amp; DCF'!L$158</f>
         <v>2979.06585633045</v>
       </c>
-      <c r="G39" s="41" t="n">
+      <c r="G39" s="53" t="n">
         <f aca="false">F39*(1+$N39)^'Financial Model &amp; DCF'!M$147-'Financial Model &amp; DCF'!M$158</f>
         <v>3174.90019869042</v>
       </c>
-      <c r="H39" s="41" t="n">
+      <c r="H39" s="53" t="n">
         <f aca="false">G39*(1+$N39)^'Financial Model &amp; DCF'!N$147-'Financial Model &amp; DCF'!N$158</f>
         <v>3366.21520390801</v>
       </c>
-      <c r="I39" s="41" t="n">
+      <c r="I39" s="53" t="n">
         <f aca="false">H39*(1+$N39)^'Financial Model &amp; DCF'!O$147-'Financial Model &amp; DCF'!O$158</f>
         <v>3552.00416292529</v>
       </c>
-      <c r="J39" s="41" t="n">
+      <c r="J39" s="53" t="n">
         <f aca="false">I39*(1+$N39)^'Financial Model &amp; DCF'!P$147-'Financial Model &amp; DCF'!P$158</f>
         <v>3734.13918985422</v>
       </c>
-      <c r="K39" s="41" t="n">
+      <c r="K39" s="53" t="n">
         <f aca="false">J39*(1+$N39)^'Financial Model &amp; DCF'!Q$147-'Financial Model &amp; DCF'!Q$158</f>
         <v>3918.04764009464</v>
       </c>
-      <c r="L39" s="41" t="n">
+      <c r="L39" s="53" t="n">
         <f aca="false">K39*(1+$N39)^'Financial Model &amp; DCF'!R$147-'Financial Model &amp; DCF'!R$158</f>
         <v>4103.21121701399</v>
       </c>
@@ -12557,9 +12096,9 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="B40" s="25" t="n">
         <f aca="false">(B39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12587,7 +12126,7 @@
       </c>
       <c r="H40" s="25" t="n">
         <f aca="false">(H39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>310.147550795575</v>
+        <v>310.147550795576</v>
       </c>
       <c r="I40" s="25" t="n">
         <f aca="false">(I39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12599,58 +12138,58 @@
       </c>
       <c r="K40" s="25" t="n">
         <f aca="false">(K39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>361.447396122956</v>
+        <v>361.447396122957</v>
       </c>
       <c r="L40" s="25" t="n">
         <f aca="false">(L39-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
         <v>378.660706239099</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B41" s="41" t="n">
+        <v>265</v>
+      </c>
+      <c r="B41" s="53" t="n">
         <f aca="false">SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$N41)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+$O41)/($N41-$O41)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$N41)^-'Financial Model &amp; DCF'!$R$148</f>
         <v>3148.26586103396</v>
       </c>
-      <c r="C41" s="41" t="n">
+      <c r="C41" s="53" t="n">
         <f aca="false">B41*(1+$N41)^'Financial Model &amp; DCF'!I$147-'Financial Model &amp; DCF'!I$158</f>
-        <v>3258.09747281942</v>
-      </c>
-      <c r="D41" s="41" t="n">
+        <v>3258.09747281943</v>
+      </c>
+      <c r="D41" s="53" t="n">
         <f aca="false">C41*(1+$N41)^'Financial Model &amp; DCF'!J$147-'Financial Model &amp; DCF'!J$158</f>
         <v>3490.22459114851</v>
       </c>
-      <c r="E41" s="41" t="n">
+      <c r="E41" s="53" t="n">
         <f aca="false">D41*(1+$N41)^'Financial Model &amp; DCF'!K$147-'Financial Model &amp; DCF'!K$158</f>
         <v>3718.64164200653</v>
       </c>
-      <c r="F41" s="41" t="n">
+      <c r="F41" s="53" t="n">
         <f aca="false">E41*(1+$N41)^'Financial Model &amp; DCF'!L$147-'Financial Model &amp; DCF'!L$158</f>
         <v>3942.36455333481</v>
       </c>
-      <c r="G41" s="41" t="n">
+      <c r="G41" s="53" t="n">
         <f aca="false">F41*(1+$N41)^'Financial Model &amp; DCF'!M$147-'Financial Model &amp; DCF'!M$158</f>
         <v>4160.49796781355</v>
       </c>
-      <c r="H41" s="41" t="n">
+      <c r="H41" s="53" t="n">
         <f aca="false">G41*(1+$N41)^'Financial Model &amp; DCF'!N$147-'Financial Model &amp; DCF'!N$158</f>
         <v>4372.09077943279</v>
       </c>
-      <c r="I41" s="41" t="n">
+      <c r="I41" s="53" t="n">
         <f aca="false">H41*(1+$N41)^'Financial Model &amp; DCF'!O$147-'Financial Model &amp; DCF'!O$158</f>
-        <v>4576.05485829151</v>
-      </c>
-      <c r="J41" s="41" t="n">
+        <v>4576.05485829152</v>
+      </c>
+      <c r="J41" s="53" t="n">
         <f aca="false">I41*(1+$N41)^'Financial Model &amp; DCF'!P$147-'Financial Model &amp; DCF'!P$158</f>
         <v>4774.19411106807</v>
       </c>
-      <c r="K41" s="41" t="n">
+      <c r="K41" s="53" t="n">
         <f aca="false">J41*(1+$N41)^'Financial Model &amp; DCF'!Q$147-'Financial Model &amp; DCF'!Q$158</f>
         <v>4971.82444581459</v>
       </c>
-      <c r="L41" s="41" t="n">
+      <c r="L41" s="53" t="n">
         <f aca="false">K41*(1+$N41)^'Financial Model &amp; DCF'!R$147-'Financial Model &amp; DCF'!R$158</f>
         <v>5168.19809841823</v>
       </c>
@@ -12666,9 +12205,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="B42" s="25" t="n">
         <f aca="false">(B41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12684,7 +12223,7 @@
       </c>
       <c r="E42" s="25" t="n">
         <f aca="false">(E41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>342.910071767828</v>
+        <v>342.910071767829</v>
       </c>
       <c r="F42" s="25" t="n">
         <f aca="false">(F41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12700,7 +12239,7 @@
       </c>
       <c r="I42" s="25" t="n">
         <f aca="false">(I41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
-        <v>422.617538188297</v>
+        <v>422.617538188298</v>
       </c>
       <c r="J42" s="25" t="n">
         <f aca="false">(J41-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12715,51 +12254,51 @@
         <v>477.664785573881</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B43" s="41" t="n">
+        <v>267</v>
+      </c>
+      <c r="B43" s="53" t="n">
         <f aca="false">SUMPRODUCT('Financial Model &amp; DCF'!$I$158:$R$158,(1+$N43)^-('Financial Model &amp; DCF'!$I$148:$R$148))+(('Financial Model &amp; DCF'!$R$156*(1+$O43)/($N43-$O43)+'Financial Model &amp; DCF'!$D$139*('Financial Model &amp; DCF'!$R$151+'Financial Model &amp; DCF'!$R$153))/2)*(1+$N43)^-'Financial Model &amp; DCF'!$R$148</f>
         <v>6033.05806019508</v>
       </c>
-      <c r="C43" s="41" t="n">
+      <c r="C43" s="53" t="n">
         <f aca="false">B43*(1+$N43)^'Financial Model &amp; DCF'!I$147-'Financial Model &amp; DCF'!I$158</f>
         <v>6199.85874330352</v>
       </c>
-      <c r="D43" s="41" t="n">
+      <c r="D43" s="53" t="n">
         <f aca="false">C43*(1+$N43)^'Financial Model &amp; DCF'!J$147-'Financial Model &amp; DCF'!J$158</f>
         <v>6558.03839475768</v>
       </c>
-      <c r="E43" s="41" t="n">
+      <c r="E43" s="53" t="n">
         <f aca="false">D43*(1+$N43)^'Financial Model &amp; DCF'!K$147-'Financial Model &amp; DCF'!K$158</f>
         <v>6916.05885102733</v>
       </c>
-      <c r="F43" s="41" t="n">
+      <c r="F43" s="53" t="n">
         <f aca="false">E43*(1+$N43)^'Financial Model &amp; DCF'!L$147-'Financial Model &amp; DCF'!L$158</f>
         <v>7273.24104810183</v>
       </c>
-      <c r="G43" s="41" t="n">
+      <c r="G43" s="53" t="n">
         <f aca="false">F43*(1+$N43)^'Financial Model &amp; DCF'!M$147-'Financial Model &amp; DCF'!M$158</f>
         <v>7629.03414367372</v>
       </c>
-      <c r="H43" s="41" t="n">
+      <c r="H43" s="53" t="n">
         <f aca="false">G43*(1+$N43)^'Financial Model &amp; DCF'!N$147-'Financial Model &amp; DCF'!N$158</f>
         <v>7982.8718473676</v>
       </c>
-      <c r="I43" s="41" t="n">
+      <c r="I43" s="53" t="n">
         <f aca="false">H43*(1+$N43)^'Financial Model &amp; DCF'!O$147-'Financial Model &amp; DCF'!O$158</f>
         <v>8334.09488005344</v>
       </c>
-      <c r="J43" s="41" t="n">
+      <c r="J43" s="53" t="n">
         <f aca="false">I43*(1+$N43)^'Financial Model &amp; DCF'!P$147-'Financial Model &amp; DCF'!P$158</f>
         <v>8684.98563707868</v>
       </c>
-      <c r="K43" s="41" t="n">
+      <c r="K43" s="53" t="n">
         <f aca="false">J43*(1+$N43)^'Financial Model &amp; DCF'!Q$147-'Financial Model &amp; DCF'!Q$158</f>
         <v>9041.33353879453</v>
       </c>
-      <c r="L43" s="41" t="n">
+      <c r="L43" s="53" t="n">
         <f aca="false">K43*(1+$N43)^'Financial Model &amp; DCF'!R$147-'Financial Model &amp; DCF'!R$158</f>
         <v>9402.78879352558</v>
       </c>
@@ -12775,9 +12314,9 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="B44" s="25" t="n">
         <f aca="false">(B43-('Financial Model &amp; DCF'!$H$52-'Financial Model &amp; DCF'!$H$44))/'Financial Model &amp; DCF'!$D$136</f>
@@ -12824,98 +12363,76 @@
         <v>871.323862928845</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="B45" s="55" t="n">
+        <v>269</v>
+      </c>
+      <c r="B45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="C45" s="55" t="n">
+      <c r="C45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="D45" s="55" t="n">
+      <c r="D45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="E45" s="55" t="n">
+      <c r="E45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="F45" s="55" t="n">
+      <c r="F45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="G45" s="55" t="n">
+      <c r="G45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="H45" s="55" t="n">
+      <c r="H45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="I45" s="55" t="n">
+      <c r="I45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="J45" s="55" t="n">
+      <c r="J45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="K45" s="55" t="n">
+      <c r="K45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
-      <c r="L45" s="55" t="n">
+      <c r="L45" s="54" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$135</f>
         <v>247.23</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="B46" s="25" t="n">
         <f aca="false">B40*$P$39+B42*$P$41+B44*$P$43</f>
         <v>336.669287908282</v>
       </c>
-      <c r="P46" s="43" t="n">
+      <c r="P46" s="55" t="n">
         <f aca="false">P39+P41+P43</f>
         <v>1</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>271</v>
+      </c>
+    </row>
     <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -12927,68 +12444,66 @@
       <c r="I70" s="16"/>
       <c r="J70" s="16"/>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="B72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="B73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="B74" s="22" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$136+B72</f>
         <v>10.757</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="B75" s="22" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$170+B73</f>
         <v>2961.57574812283</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="B76" s="25" t="n">
         <f aca="false">B75/B74</f>
         <v>275.316142802159</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="B77" s="39" t="n">
         <f aca="false">B76/'Financial Model &amp; DCF'!$D$135-1</f>
         <v>0.113603295725273</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="80" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -13000,53 +12515,49 @@
       <c r="I80" s="16"/>
       <c r="J80" s="16"/>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>288</v>
+      </c>
+    </row>
     <row r="93" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="15" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
@@ -13058,39 +12569,24 @@
       <c r="I93" s="16"/>
       <c r="J93" s="16"/>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="56" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>292</v>
+      </c>
+    </row>
     <row r="112" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
@@ -13102,40 +12598,40 @@
       <c r="I112" s="16"/>
       <c r="J112" s="16"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="B114" s="21" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="B115" s="22" t="n">
         <f aca="false">-'Financial Model &amp; DCF'!$D$135*(1+B114)*'Financial Model &amp; DCF'!$D$136</f>
         <v>-2659.45311</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="B116" s="32" t="n">
         <f aca="false">'Financial Model &amp; DCF'!$D$139</f>
         <v>13</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="B117" s="22" t="n">
         <f aca="false">B115</f>
@@ -13182,58 +12678,57 @@
         <v>5917.53916510176</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="B118" s="40" t="n">
         <f aca="false">IFERROR(IRR(B117:L117),"n/m - owner cash flows never turn positive")</f>
         <v>0.0832654213234738</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="B119" s="57" t="n">
         <f aca="false">SUM(C117:L117)/-B115</f>
         <v>2.22509625864461</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="51" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="49" t="n">
         <f aca="false">$B$116+-2</f>
         <v>11</v>
       </c>
-      <c r="C123" s="51" t="n">
+      <c r="C123" s="49" t="n">
         <f aca="false">$B$116+-1</f>
         <v>12</v>
       </c>
-      <c r="D123" s="51" t="n">
+      <c r="D123" s="49" t="n">
         <f aca="false">$B$116+0</f>
         <v>13</v>
       </c>
-      <c r="E123" s="51" t="n">
+      <c r="E123" s="49" t="n">
         <f aca="false">$B$116+1</f>
         <v>14</v>
       </c>
-      <c r="F123" s="51" t="n">
+      <c r="F123" s="49" t="n">
         <f aca="false">$B$116+2</f>
         <v>15</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="40" t="n">
         <v>-0.2</v>
       </c>
@@ -13258,7 +12753,7 @@
         <v>0.120528474218776</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="40" t="n">
         <v>-0.1</v>
       </c>
@@ -13283,7 +12778,7 @@
         <v>0.107407970018091</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="40" t="n">
         <v>0</v>
       </c>
@@ -13308,7 +12803,7 @@
         <v>0.0958015130239514</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="40" t="n">
         <v>0.1</v>
       </c>
@@ -13333,7 +12828,7 @@
         <v>0.08540702282327</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="40" t="n">
         <v>0.2</v>
       </c>
@@ -13358,10 +12853,9 @@
         <v>0.0760037159191591</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
